--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133657369</v>
+        <v>133657367</v>
       </c>
       <c r="B4" t="n">
-        <v>97457</v>
+        <v>97421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mardyveln, i brant ca 60 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325441</v>
+        <v>325493</v>
       </c>
       <c r="R4" t="n">
-        <v>6556279</v>
+        <v>6556414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,52 +989,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133657367</v>
+        <v>133657369</v>
       </c>
       <c r="B5" t="n">
-        <v>97421</v>
+        <v>97457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant ca 60 m norr om, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325493</v>
+        <v>325441</v>
       </c>
       <c r="R5" t="n">
-        <v>6556414</v>
+        <v>6556279</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133657373</v>
+        <v>133657356</v>
       </c>
       <c r="B7" t="n">
-        <v>97421</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 125 m söder om, Dls</t>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325571</v>
+        <v>325284</v>
       </c>
       <c r="R7" t="n">
-        <v>6556049</v>
+        <v>6556743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,6 +1283,11 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1294,12 +1299,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
+          <t>Tallskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133657356</v>
+        <v>133657373</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>97421</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mardyveln, ca 125 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325284</v>
+        <v>325571</v>
       </c>
       <c r="R8" t="n">
-        <v>6556743</v>
+        <v>6556049</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,11 +1390,6 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1406,7 +1401,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1852,45 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133657370</v>
+        <v>133659796</v>
       </c>
       <c r="B13" t="n">
-        <v>97421</v>
+        <v>4776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325441</v>
+        <v>325488</v>
       </c>
       <c r="R13" t="n">
-        <v>6556279</v>
+        <v>6556147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>På murken granlåga.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1952,14 +1952,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133657371</v>
+        <v>133657370</v>
       </c>
       <c r="B14" t="n">
         <v>97421</v>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant SV om, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325458</v>
+        <v>325441</v>
       </c>
       <c r="R14" t="n">
-        <v>6556181</v>
+        <v>6556279</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,52 +2059,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133659796</v>
+        <v>133657371</v>
       </c>
       <c r="B15" t="n">
-        <v>4776</v>
+        <v>97421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mardyveln, i brant SV om, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325488</v>
+        <v>325458</v>
       </c>
       <c r="R15" t="n">
-        <v>6556147</v>
+        <v>6556181</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133657374</v>
       </c>
       <c r="B2" t="n">
-        <v>97430</v>
+        <v>97437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133657367</v>
       </c>
       <c r="B4" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133657369</v>
       </c>
       <c r="B5" t="n">
-        <v>97457</v>
+        <v>97464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133657376</v>
       </c>
       <c r="B6" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133657356</v>
+        <v>133657373</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>97428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mardyveln, ca 125 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325284</v>
+        <v>325571</v>
       </c>
       <c r="R7" t="n">
-        <v>6556743</v>
+        <v>6556049</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,11 +1283,6 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1299,7 +1294,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133657373</v>
+        <v>133657356</v>
       </c>
       <c r="B8" t="n">
-        <v>97421</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 125 m söder om, Dls</t>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325571</v>
+        <v>325284</v>
       </c>
       <c r="R8" t="n">
-        <v>6556049</v>
+        <v>6556743</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1390,11 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1401,12 +1406,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
+          <t>Tallskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>133657372</v>
       </c>
       <c r="B9" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>133657368</v>
       </c>
       <c r="B10" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>133657378</v>
       </c>
       <c r="B11" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>133657375</v>
       </c>
       <c r="B12" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133657370</v>
+        <v>133657371</v>
       </c>
       <c r="B14" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mardyveln, i brant SV om, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325441</v>
+        <v>325458</v>
       </c>
       <c r="R14" t="n">
-        <v>6556279</v>
+        <v>6556181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,17 +2059,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133657371</v>
+        <v>133657370</v>
       </c>
       <c r="B15" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant SV om, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325458</v>
+        <v>325441</v>
       </c>
       <c r="R15" t="n">
-        <v>6556181</v>
+        <v>6556279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
         <v>133657355</v>
       </c>
       <c r="B18" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>134246089</v>
       </c>
       <c r="B19" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>134246315</v>
       </c>
       <c r="B20" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>134245975</v>
       </c>
       <c r="B21" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>134246151</v>
       </c>
       <c r="B22" t="n">
-        <v>97796</v>
+        <v>97803</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>134288659</v>
       </c>
       <c r="B23" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>134288151</v>
       </c>
       <c r="B24" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133657374</v>
+        <v>133657367</v>
       </c>
       <c r="B2" t="n">
-        <v>97437</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>291</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbtrådmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis catenulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 125 m söder om, Dls</t>
+          <t>Mardyveln, i brant ca 60 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325550</v>
+        <v>325493</v>
       </c>
       <c r="R2" t="n">
-        <v>6556054</v>
+        <v>6556414</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133657357</v>
+        <v>133657370</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325321</v>
+        <v>325441</v>
       </c>
       <c r="R3" t="n">
-        <v>6556585</v>
+        <v>6556279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +855,6 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,7 +866,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133657367</v>
+        <v>133657371</v>
       </c>
       <c r="B4" t="n">
-        <v>97428</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant ca 60 m norr om, Dls</t>
+          <t>Mardyveln, i brant SV om, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325493</v>
+        <v>325458</v>
       </c>
       <c r="R4" t="n">
-        <v>6556414</v>
+        <v>6556181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,45 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133657369</v>
+        <v>133657372</v>
       </c>
       <c r="B5" t="n">
-        <v>97464</v>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325441</v>
+        <v>325488</v>
       </c>
       <c r="R5" t="n">
-        <v>6556279</v>
+        <v>6556147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133657376</v>
+        <v>133657373</v>
       </c>
       <c r="B6" t="n">
-        <v>97428</v>
+        <v>97435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,14 +1134,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 75 m söder om, Dls</t>
+          <t>Mardyveln, ca 125 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325527</v>
+        <v>325571</v>
       </c>
       <c r="R6" t="n">
-        <v>6556094</v>
+        <v>6556049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133657373</v>
+        <v>133657375</v>
       </c>
       <c r="B7" t="n">
-        <v>97428</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325571</v>
+        <v>325550</v>
       </c>
       <c r="R7" t="n">
-        <v>6556049</v>
+        <v>6556054</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133657356</v>
+        <v>133657376</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>97435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mardyveln, ca 75 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325284</v>
+        <v>325527</v>
       </c>
       <c r="R8" t="n">
-        <v>6556743</v>
+        <v>6556094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,11 +1390,6 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1406,7 +1401,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133657372</v>
+        <v>133657378</v>
       </c>
       <c r="B9" t="n">
-        <v>97428</v>
+        <v>97435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,14 +1455,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mardyveln, ca 50 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325488</v>
+        <v>325520</v>
       </c>
       <c r="R9" t="n">
-        <v>6556147</v>
+        <v>6556115</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,45 +1531,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133657368</v>
+        <v>134245929</v>
       </c>
       <c r="B10" t="n">
-        <v>96776</v>
+        <v>97435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Nordväst Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325446</v>
+        <v>325012</v>
       </c>
       <c r="R10" t="n">
-        <v>6556299</v>
+        <v>6557220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,17 +1600,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Många riktigt stora tuvor mellan branten och tjärnet.</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,33 +1614,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133657378</v>
+        <v>134288151</v>
       </c>
       <c r="B11" t="n">
-        <v>97428</v>
+        <v>97435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,16 +1662,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 50 m söder om, Dls</t>
+          <t>Nordväst på Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325520</v>
+        <v>325074</v>
       </c>
       <c r="R11" t="n">
-        <v>6556115</v>
+        <v>6557151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,12 +1702,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,38 +1716,49 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På murken granlåga.</t>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133657375</v>
+        <v>133657374</v>
       </c>
       <c r="B12" t="n">
-        <v>97428</v>
+        <v>97444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,17 +1855,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133659796</v>
+        <v>134246003</v>
       </c>
       <c r="B13" t="n">
-        <v>4776</v>
+        <v>83343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1873,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325488</v>
+        <v>325114</v>
       </c>
       <c r="R13" t="n">
-        <v>6556147</v>
+        <v>6557125</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,12 +1938,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På ved av alstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,38 +1957,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133657371</v>
+        <v>134246315</v>
       </c>
       <c r="B14" t="n">
-        <v>97428</v>
+        <v>83350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1987,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant SV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325458</v>
+        <v>325181</v>
       </c>
       <c r="R14" t="n">
-        <v>6556181</v>
+        <v>6556975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,12 +2044,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På ved av klibbal i sumpskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,38 +2063,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133657370</v>
+        <v>134287964</v>
       </c>
       <c r="B15" t="n">
-        <v>97428</v>
+        <v>92013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,34 +2093,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325441</v>
+        <v>325404</v>
       </c>
       <c r="R15" t="n">
-        <v>6556279</v>
+        <v>6556569</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,12 +2154,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,38 +2168,49 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På murken granlåga.</t>
+          <t>Låga med markkontakt, på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133696600</v>
+        <v>133657368</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>96783</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,49 +2218,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325266</v>
+        <v>325446</v>
       </c>
       <c r="R16" t="n">
-        <v>6556841</v>
+        <v>6556299</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2250,12 +2272,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Många riktigt stora tuvor mellan branten och tjärnet.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,62 +2293,59 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133696603</v>
+        <v>134246151</v>
       </c>
       <c r="B17" t="n">
-        <v>58461</v>
+        <v>97810</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,13 +2353,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325266</v>
+        <v>325171</v>
       </c>
       <c r="R17" t="n">
-        <v>6556841</v>
+        <v>6556959</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2359,12 +2383,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,6 +2397,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2391,10 +2416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133657355</v>
+        <v>133657369</v>
       </c>
       <c r="B18" t="n">
-        <v>93264</v>
+        <v>97471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,37 +2427,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325121</v>
+        <v>325441</v>
       </c>
       <c r="R18" t="n">
-        <v>6556881</v>
+        <v>6556279</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,13 +2495,17 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2497,48 +2523,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134246089</v>
+        <v>133657362</v>
       </c>
       <c r="B19" t="n">
-        <v>79985</v>
+        <v>97873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2609</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325136</v>
+        <v>325499</v>
       </c>
       <c r="R19" t="n">
-        <v>6557020</v>
+        <v>6556462</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,12 +2588,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,67 +2602,68 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Bergbrant i barrskog.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134246315</v>
+        <v>133657365</v>
       </c>
       <c r="B20" t="n">
-        <v>83343</v>
+        <v>96512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325181</v>
+        <v>325499</v>
       </c>
       <c r="R20" t="n">
-        <v>6556975</v>
+        <v>6556462</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,17 +2690,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På ved av klibbal i sumpskog</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,33 +2704,37 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Bergbrant i barrskog.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134245975</v>
+        <v>133657355</v>
       </c>
       <c r="B21" t="n">
-        <v>93264</v>
+        <v>93271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2738,14 +2761,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325056</v>
+        <v>325121</v>
       </c>
       <c r="R21" t="n">
-        <v>6557097</v>
+        <v>6556881</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,17 +2795,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,53 +2813,57 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134246151</v>
+        <v>134245975</v>
       </c>
       <c r="B22" t="n">
-        <v>97803</v>
+        <v>93271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2569</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2849,10 +2871,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325171</v>
+        <v>325056</v>
       </c>
       <c r="R22" t="n">
-        <v>6556959</v>
+        <v>6557097</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,6 +2907,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2939,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134288659</v>
+        <v>134245897</v>
       </c>
       <c r="B23" t="n">
-        <v>79985</v>
+        <v>75468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,44 +2950,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ravin nordväst, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325338</v>
+        <v>325008</v>
       </c>
       <c r="R23" t="n">
-        <v>6556520</v>
+        <v>6557270</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2984,12 +3007,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,45 +3025,25 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134288151</v>
+        <v>134246089</v>
       </c>
       <c r="B24" t="n">
-        <v>97428</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3048,38 +3051,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nordväst på Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325074</v>
+        <v>325136</v>
       </c>
       <c r="R24" t="n">
-        <v>6557151</v>
+        <v>6557020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,12 +3108,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,38 +3126,898 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134288659</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>325338</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6556520</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Bård E. Andersen</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Bård E. Andersen</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133657356</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>325284</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6556743</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133657357</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>325321</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6556585</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134246027</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>325114</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6557125</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133696600</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>325266</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6556841</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133659796</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>325488</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6556147</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134246129</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>325208</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6556981</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133696603</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>325266</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6556841</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133657374</v>
+        <v>134493918</v>
       </c>
       <c r="B12" t="n">
-        <v>97444</v>
+        <v>97435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>291</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbtrådmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis catenulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 125 m söder om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325550</v>
+        <v>325536</v>
       </c>
       <c r="R12" t="n">
-        <v>6556054</v>
+        <v>6556078</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1836,85 +1836,64 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134246003</v>
+        <v>134493922</v>
       </c>
       <c r="B13" t="n">
-        <v>83343</v>
+        <v>97435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>306</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325114</v>
+        <v>325481</v>
       </c>
       <c r="R13" t="n">
-        <v>6557125</v>
+        <v>6556144</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,17 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På ved av alstubbe</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,29 +1931,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134246315</v>
+        <v>134493924</v>
       </c>
       <c r="B14" t="n">
-        <v>83350</v>
+        <v>97435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,40 +1960,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325181</v>
+        <v>325468</v>
       </c>
       <c r="R14" t="n">
-        <v>6556975</v>
+        <v>6556164</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,17 +2014,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På ved av klibbal i sumpskog</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,29 +2028,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134287964</v>
+        <v>134493926</v>
       </c>
       <c r="B15" t="n">
-        <v>92013</v>
+        <v>97435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,44 +2057,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325404</v>
+        <v>325454</v>
       </c>
       <c r="R15" t="n">
-        <v>6556569</v>
+        <v>6556182</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2154,12 +2111,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,87 +2125,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt, på undersidan # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133657368</v>
+        <v>134493928</v>
       </c>
       <c r="B16" t="n">
-        <v>96783</v>
+        <v>97435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325446</v>
+        <v>325422</v>
       </c>
       <c r="R16" t="n">
-        <v>6556299</v>
+        <v>6556257</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,17 +2208,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Många riktigt stora tuvor mellan branten och tjärnet.</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,73 +2224,64 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134246151</v>
+        <v>134493931</v>
       </c>
       <c r="B17" t="n">
-        <v>97810</v>
+        <v>97435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325171</v>
+        <v>325481</v>
       </c>
       <c r="R17" t="n">
-        <v>6556959</v>
+        <v>6556410</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2383,12 +2305,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,67 +2319,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133657369</v>
+        <v>134493933</v>
       </c>
       <c r="B18" t="n">
-        <v>97471</v>
+        <v>97435</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325441</v>
+        <v>325402</v>
       </c>
       <c r="R18" t="n">
-        <v>6556279</v>
+        <v>6556504</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,12 +2402,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,74 +2418,64 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133657362</v>
+        <v>134493934</v>
       </c>
       <c r="B19" t="n">
-        <v>97873</v>
+        <v>97435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2609</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325499</v>
+        <v>325417</v>
       </c>
       <c r="R19" t="n">
-        <v>6556462</v>
+        <v>6556506</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,12 +2499,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,68 +2516,78 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Bergbrant i barrskog.</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133657365</v>
+        <v>134493935</v>
       </c>
       <c r="B20" t="n">
-        <v>96512</v>
+        <v>97435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2667</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325499</v>
+        <v>325433</v>
       </c>
       <c r="R20" t="n">
-        <v>6556462</v>
+        <v>6556589</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,12 +2611,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,30 +2628,40 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Bergbrant i barrskog.</t>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133657355</v>
+        <v>134493941</v>
       </c>
       <c r="B21" t="n">
-        <v>93271</v>
+        <v>97435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,40 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325121</v>
+        <v>325379</v>
       </c>
       <c r="R21" t="n">
-        <v>6556881</v>
+        <v>6556611</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2795,12 +2723,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,34 +2737,43 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tallskog.</t>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134245975</v>
+        <v>134493925</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>85592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,40 +2781,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>241</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325056</v>
+        <v>325455</v>
       </c>
       <c r="R22" t="n">
-        <v>6557097</v>
+        <v>6556165</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2901,17 +2835,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,29 +2849,43 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134245897</v>
+        <v>133657374</v>
       </c>
       <c r="B23" t="n">
-        <v>75468</v>
+        <v>97444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2950,40 +2893,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ravin nordväst, Dls</t>
+          <t>Mardyveln, ca 125 m söder om, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325008</v>
+        <v>325550</v>
       </c>
       <c r="R23" t="n">
-        <v>6557270</v>
+        <v>6556054</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3007,12 +2947,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,55 +2961,72 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134246089</v>
+        <v>134246003</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>83343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3078,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325136</v>
+        <v>325114</v>
       </c>
       <c r="R24" t="n">
-        <v>6557020</v>
+        <v>6557125</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,6 +3071,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På ved av alstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134288659</v>
+        <v>134246315</v>
       </c>
       <c r="B25" t="n">
-        <v>79992</v>
+        <v>83350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3152,29 +3114,25 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3183,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>325338</v>
+        <v>325181</v>
       </c>
       <c r="R25" t="n">
-        <v>6556520</v>
+        <v>6556975</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,12 +3171,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På ved av klibbal i sumpskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,80 +3194,67 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133657356</v>
+        <v>134287964</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>92013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325284</v>
+        <v>325404</v>
       </c>
       <c r="R26" t="n">
-        <v>6556743</v>
+        <v>6556569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3331,17 +3281,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,33 +3295,49 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt, på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133657357</v>
+        <v>133657368</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>96783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,34 +3345,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325321</v>
+        <v>325446</v>
       </c>
       <c r="R27" t="n">
-        <v>6556585</v>
+        <v>6556299</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3448,7 +3409,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>Många riktigt stora tuvor mellan branten och tjärnet.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,7 +3423,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3480,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134246027</v>
+        <v>134246151</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>97810</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,35 +3452,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3527,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>325114</v>
+        <v>325171</v>
       </c>
       <c r="R28" t="n">
-        <v>6557125</v>
+        <v>6556959</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,6 +3524,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3589,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133696600</v>
+        <v>133657369</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>97471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,49 +3554,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>325266</v>
+        <v>325441</v>
       </c>
       <c r="R29" t="n">
-        <v>6556841</v>
+        <v>6556279</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3666,12 +3608,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3682,26 +3624,36 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133659796</v>
+        <v>134493923</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>97471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3709,37 +3661,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>325488</v>
+        <v>325481</v>
       </c>
       <c r="R30" t="n">
-        <v>6556147</v>
+        <v>6556144</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3763,12 +3715,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,36 +3731,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134246129</v>
+        <v>134493927</v>
       </c>
       <c r="B31" t="n">
-        <v>4776</v>
+        <v>97471</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3816,46 +3758,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>325208</v>
+        <v>325443</v>
       </c>
       <c r="R31" t="n">
-        <v>6556981</v>
+        <v>6556199</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3879,12 +3812,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3893,29 +3826,43 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133696603</v>
+        <v>133657362</v>
       </c>
       <c r="B32" t="n">
-        <v>58461</v>
+        <v>97873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3923,49 +3870,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103018</v>
+        <v>2609</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325266</v>
+        <v>325499</v>
       </c>
       <c r="R32" t="n">
-        <v>6556841</v>
+        <v>6556462</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3989,12 +3924,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,19 +3940,3391 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Bergbrant i barrskog.</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133657365</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96512</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>325499</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6556462</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Bergbrant i barrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133657355</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>325121</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6556881</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134245975</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>325056</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6557097</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Roger Gran</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Roger Gran</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134493938</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>325374</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6556523</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134493945</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>325222</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6556974</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134493946</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>325214</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6556988</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134493948</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>325140</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6557024</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134493950</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>325105</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6557056</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134493939</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>325361</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6556573</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134493930</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>325481</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6556387</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134245897</v>
+      </c>
+      <c r="B43" t="n">
+        <v>75468</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, ravin nordväst, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>325008</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6557270</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134246089</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>325136</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6557020</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134288659</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>325338</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6556520</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134493940</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>325365</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6556582</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134493949</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>325128</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6557028</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>133657356</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>325284</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6556743</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>133657357</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>325321</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6556585</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134246027</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>325114</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6557125</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>133696600</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>325266</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6556841</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133659796</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>325488</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6556147</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134246129</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>325208</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6556981</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134493920</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>325483</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6556127</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134493951</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>325037</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6557099</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133696603</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>325266</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6556841</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134493919</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>325523</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6556083</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134493921</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>325483</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6556127</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134493929</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>325481</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6556387</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134493932</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>325436</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6556446</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134493937</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>325438</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6556553</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134493947</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>325197</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6556991</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657370</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657372</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657373</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657375</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657376</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657378</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134245929</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134288151</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493918</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493922</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493924</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493926</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493928</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2334,6 +2414,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493931</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493933</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493934</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2655,6 +2750,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493935</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2767,6 +2867,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493941</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2879,6 +2984,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493925</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657374</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3100,6 +3215,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246003</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3206,6 +3326,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246315</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3331,6 +3456,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134287964</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3438,6 +3568,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657368</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246151</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3647,6 +3787,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657369</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3744,6 +3889,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493923</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3856,6 +4006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493927</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3958,6 +4113,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657362</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4060,6 +4220,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657365</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4166,6 +4331,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657355</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4272,6 +4442,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134245975</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4369,6 +4544,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493938</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4466,6 +4646,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493945</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4563,6 +4748,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493946</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4660,6 +4850,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493948</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4757,6 +4952,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493950</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4869,6 +5069,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493939</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4981,6 +5186,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493930</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5082,6 +5292,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134245897</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5183,6 +5398,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246089</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5308,6 +5528,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134288659</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5420,6 +5645,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493940</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5532,6 +5762,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493949</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5639,6 +5874,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657356</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5746,6 +5986,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133657357</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5855,6 +6100,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246027</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5964,6 +6214,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696600</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6071,6 +6326,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133659796</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6178,6 +6438,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246129</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6295,6 +6560,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493920</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6412,6 +6682,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493951</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6521,6 +6796,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696603</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6638,6 +6918,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493919</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6755,6 +7040,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493921</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6872,6 +7162,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493929</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6989,6 +7284,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493932</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7106,6 +7406,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493937</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7223,6 +7528,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493947</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7325,8 +7635,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ63"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133696600</v>
+        <v>133659796</v>
       </c>
       <c r="B51" t="n">
-        <v>57162</v>
+        <v>4776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,49 +6119,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325266</v>
+        <v>325488</v>
       </c>
       <c r="R51" t="n">
-        <v>6556841</v>
+        <v>6556147</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6185,12 +6173,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6201,28 +6189,38 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133659796</v>
+        <v>134246129</v>
       </c>
       <c r="B52" t="n">
         <v>4776</v>
@@ -6251,16 +6249,25 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325488</v>
+        <v>325208</v>
       </c>
       <c r="R52" t="n">
-        <v>6556147</v>
+        <v>6556981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6287,12 +6294,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6301,43 +6308,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246129</v>
+        <v>134493920</v>
       </c>
       <c r="B53" t="n">
-        <v>4776</v>
+        <v>5181</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6345,46 +6343,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325208</v>
+        <v>325483</v>
       </c>
       <c r="R53" t="n">
-        <v>6556981</v>
+        <v>6556127</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6408,12 +6402,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,31 +6416,45 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493920</v>
+        <v>134493951</v>
       </c>
       <c r="B54" t="n">
         <v>5181</v>
@@ -6486,10 +6494,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325483</v>
+        <v>325037</v>
       </c>
       <c r="R54" t="n">
-        <v>6556127</v>
+        <v>6557099</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6562,16 +6570,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134493951</v>
+        <v>133696603</v>
       </c>
       <c r="B55" t="n">
-        <v>5181</v>
+        <v>58461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6579,42 +6587,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>103018</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325037</v>
+        <v>325266</v>
       </c>
       <c r="R55" t="n">
-        <v>6557099</v>
+        <v>6556841</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6638,12 +6653,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,46 +6669,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133696603</v>
+        <v>134493919</v>
       </c>
       <c r="B56" t="n">
-        <v>58461</v>
+        <v>5201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,49 +6701,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103018</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325266</v>
+        <v>325523</v>
       </c>
       <c r="R56" t="n">
-        <v>6556841</v>
+        <v>6556083</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,12 +6760,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6783,28 +6776,43 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493919</v>
+        <v>134493921</v>
       </c>
       <c r="B57" t="n">
         <v>5201</v>
@@ -6844,10 +6852,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325523</v>
+        <v>325483</v>
       </c>
       <c r="R57" t="n">
-        <v>6556083</v>
+        <v>6556127</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6920,13 +6928,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493921</v>
+        <v>134493929</v>
       </c>
       <c r="B58" t="n">
         <v>5201</v>
@@ -6966,10 +6974,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325483</v>
+        <v>325481</v>
       </c>
       <c r="R58" t="n">
-        <v>6556127</v>
+        <v>6556387</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7042,13 +7050,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493929</v>
+        <v>134493932</v>
       </c>
       <c r="B59" t="n">
         <v>5201</v>
@@ -7088,10 +7096,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325481</v>
+        <v>325436</v>
       </c>
       <c r="R59" t="n">
-        <v>6556387</v>
+        <v>6556446</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7164,13 +7172,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493932</v>
+        <v>134493937</v>
       </c>
       <c r="B60" t="n">
         <v>5201</v>
@@ -7210,10 +7218,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325436</v>
+        <v>325438</v>
       </c>
       <c r="R60" t="n">
-        <v>6556446</v>
+        <v>6556553</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7286,16 +7294,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493937</v>
+        <v>134493947</v>
       </c>
       <c r="B61" t="n">
-        <v>5201</v>
+        <v>8460</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7303,21 +7311,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7332,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325438</v>
+        <v>325197</v>
       </c>
       <c r="R61" t="n">
-        <v>6556553</v>
+        <v>6556991</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7381,17 +7389,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7408,16 +7416,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493947</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493947</v>
+        <v>134493943</v>
       </c>
       <c r="B62" t="n">
-        <v>8460</v>
+        <v>8449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,21 +7433,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7454,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325197</v>
+        <v>325364</v>
       </c>
       <c r="R62" t="n">
-        <v>6556991</v>
+        <v>6556631</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7501,21 +7509,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7529,113 +7522,6 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>134493943</v>
-      </c>
-      <c r="B63" t="n">
-        <v>8449</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Mellanfjällen, Dls</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>325364</v>
-      </c>
-      <c r="R63" t="n">
-        <v>6556631</v>
-      </c>
-      <c r="S63" t="n">
-        <v>5</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7704,7 +7590,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133659796</v>
+        <v>133696600</v>
       </c>
       <c r="B51" t="n">
-        <v>4776</v>
+        <v>57162</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,37 +6119,49 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325488</v>
+        <v>325266</v>
       </c>
       <c r="R51" t="n">
-        <v>6556147</v>
+        <v>6556841</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6173,12 +6185,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,38 +6201,28 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134246129</v>
+        <v>133659796</v>
       </c>
       <c r="B52" t="n">
         <v>4776</v>
@@ -6249,25 +6251,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325208</v>
+        <v>325488</v>
       </c>
       <c r="R52" t="n">
-        <v>6556981</v>
+        <v>6556147</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,12 +6287,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,34 +6301,43 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134493920</v>
+        <v>134246129</v>
       </c>
       <c r="B53" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,42 +6345,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325483</v>
+        <v>325208</v>
       </c>
       <c r="R53" t="n">
-        <v>6556127</v>
+        <v>6556981</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6402,12 +6408,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6416,45 +6422,31 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493951</v>
+        <v>134493920</v>
       </c>
       <c r="B54" t="n">
         <v>5181</v>
@@ -6494,10 +6486,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325037</v>
+        <v>325483</v>
       </c>
       <c r="R54" t="n">
-        <v>6557099</v>
+        <v>6556127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6570,16 +6562,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133696603</v>
+        <v>134493951</v>
       </c>
       <c r="B55" t="n">
-        <v>58461</v>
+        <v>5181</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6587,49 +6579,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103018</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325266</v>
+        <v>325037</v>
       </c>
       <c r="R55" t="n">
-        <v>6556841</v>
+        <v>6557099</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6653,12 +6638,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6669,31 +6654,46 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134493919</v>
+        <v>133696603</v>
       </c>
       <c r="B56" t="n">
-        <v>5201</v>
+        <v>58461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,42 +6701,49 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325523</v>
+        <v>325266</v>
       </c>
       <c r="R56" t="n">
-        <v>6556083</v>
+        <v>6556841</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6760,12 +6767,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,43 +6783,28 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493921</v>
+        <v>134493919</v>
       </c>
       <c r="B57" t="n">
         <v>5201</v>
@@ -6852,10 +6844,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325483</v>
+        <v>325523</v>
       </c>
       <c r="R57" t="n">
-        <v>6556127</v>
+        <v>6556083</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6928,13 +6920,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493929</v>
+        <v>134493921</v>
       </c>
       <c r="B58" t="n">
         <v>5201</v>
@@ -6974,10 +6966,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325481</v>
+        <v>325483</v>
       </c>
       <c r="R58" t="n">
-        <v>6556387</v>
+        <v>6556127</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7050,13 +7042,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493932</v>
+        <v>134493929</v>
       </c>
       <c r="B59" t="n">
         <v>5201</v>
@@ -7096,10 +7088,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325436</v>
+        <v>325481</v>
       </c>
       <c r="R59" t="n">
-        <v>6556446</v>
+        <v>6556387</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7172,13 +7164,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493937</v>
+        <v>134493932</v>
       </c>
       <c r="B60" t="n">
         <v>5201</v>
@@ -7218,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325438</v>
+        <v>325436</v>
       </c>
       <c r="R60" t="n">
-        <v>6556553</v>
+        <v>6556446</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7294,16 +7286,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493947</v>
+        <v>134493937</v>
       </c>
       <c r="B61" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7311,21 +7303,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7340,10 +7332,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325197</v>
+        <v>325438</v>
       </c>
       <c r="R61" t="n">
-        <v>6556991</v>
+        <v>6556553</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7389,17 +7381,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7416,16 +7408,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493943</v>
+        <v>134493947</v>
       </c>
       <c r="B62" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,21 +7425,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7462,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325364</v>
+        <v>325197</v>
       </c>
       <c r="R62" t="n">
-        <v>6556631</v>
+        <v>6556991</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7509,6 +7501,21 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7522,6 +7529,113 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493947</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7590,6 +7704,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -6111,7 +6111,7 @@
         <v>133696600</v>
       </c>
       <c r="B51" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ63"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133696600</v>
+        <v>133659796</v>
       </c>
       <c r="B51" t="n">
-        <v>57167</v>
+        <v>4776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,49 +6119,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325266</v>
+        <v>325488</v>
       </c>
       <c r="R51" t="n">
-        <v>6556841</v>
+        <v>6556147</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6185,12 +6173,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6201,28 +6189,38 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133659796</v>
+        <v>134246129</v>
       </c>
       <c r="B52" t="n">
         <v>4776</v>
@@ -6251,16 +6249,25 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325488</v>
+        <v>325208</v>
       </c>
       <c r="R52" t="n">
-        <v>6556147</v>
+        <v>6556981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6287,12 +6294,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6301,43 +6308,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246129</v>
+        <v>134493920</v>
       </c>
       <c r="B53" t="n">
-        <v>4776</v>
+        <v>5181</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6345,46 +6343,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325208</v>
+        <v>325483</v>
       </c>
       <c r="R53" t="n">
-        <v>6556981</v>
+        <v>6556127</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6408,12 +6402,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,31 +6416,45 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493920</v>
+        <v>134493951</v>
       </c>
       <c r="B54" t="n">
         <v>5181</v>
@@ -6486,10 +6494,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325483</v>
+        <v>325037</v>
       </c>
       <c r="R54" t="n">
-        <v>6556127</v>
+        <v>6557099</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6562,16 +6570,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134493951</v>
+        <v>133696603</v>
       </c>
       <c r="B55" t="n">
-        <v>5181</v>
+        <v>58461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6579,42 +6587,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>103018</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325037</v>
+        <v>325266</v>
       </c>
       <c r="R55" t="n">
-        <v>6557099</v>
+        <v>6556841</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6638,12 +6653,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,46 +6669,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133696603</v>
+        <v>134493919</v>
       </c>
       <c r="B56" t="n">
-        <v>58461</v>
+        <v>5201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,49 +6701,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103018</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325266</v>
+        <v>325523</v>
       </c>
       <c r="R56" t="n">
-        <v>6556841</v>
+        <v>6556083</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,12 +6760,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6783,28 +6776,43 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493919</v>
+        <v>134493921</v>
       </c>
       <c r="B57" t="n">
         <v>5201</v>
@@ -6844,10 +6852,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325523</v>
+        <v>325483</v>
       </c>
       <c r="R57" t="n">
-        <v>6556083</v>
+        <v>6556127</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6920,13 +6928,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493921</v>
+        <v>134493929</v>
       </c>
       <c r="B58" t="n">
         <v>5201</v>
@@ -6966,10 +6974,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325483</v>
+        <v>325481</v>
       </c>
       <c r="R58" t="n">
-        <v>6556127</v>
+        <v>6556387</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7042,13 +7050,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493929</v>
+        <v>134493932</v>
       </c>
       <c r="B59" t="n">
         <v>5201</v>
@@ -7088,10 +7096,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325481</v>
+        <v>325436</v>
       </c>
       <c r="R59" t="n">
-        <v>6556387</v>
+        <v>6556446</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7164,13 +7172,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493932</v>
+        <v>134493937</v>
       </c>
       <c r="B60" t="n">
         <v>5201</v>
@@ -7210,10 +7218,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325436</v>
+        <v>325438</v>
       </c>
       <c r="R60" t="n">
-        <v>6556446</v>
+        <v>6556553</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7286,16 +7294,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493937</v>
+        <v>134493947</v>
       </c>
       <c r="B61" t="n">
-        <v>5201</v>
+        <v>8460</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7303,21 +7311,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7332,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325438</v>
+        <v>325197</v>
       </c>
       <c r="R61" t="n">
-        <v>6556553</v>
+        <v>6556991</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7381,17 +7389,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7408,16 +7416,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493947</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493947</v>
+        <v>134493943</v>
       </c>
       <c r="B62" t="n">
-        <v>8460</v>
+        <v>8449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,21 +7433,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7454,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325197</v>
+        <v>325364</v>
       </c>
       <c r="R62" t="n">
-        <v>6556991</v>
+        <v>6556631</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7501,21 +7509,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7529,113 +7522,6 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>134493943</v>
-      </c>
-      <c r="B63" t="n">
-        <v>8449</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Mellanfjällen, Dls</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>325364</v>
-      </c>
-      <c r="R63" t="n">
-        <v>6556631</v>
-      </c>
-      <c r="S63" t="n">
-        <v>5</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7704,7 +7590,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133659796</v>
+        <v>133696600</v>
       </c>
       <c r="B51" t="n">
-        <v>4776</v>
+        <v>57167</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,37 +6119,49 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325488</v>
+        <v>325266</v>
       </c>
       <c r="R51" t="n">
-        <v>6556147</v>
+        <v>6556841</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6173,12 +6185,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,38 +6201,28 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134246129</v>
+        <v>133659796</v>
       </c>
       <c r="B52" t="n">
         <v>4776</v>
@@ -6249,25 +6251,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325208</v>
+        <v>325488</v>
       </c>
       <c r="R52" t="n">
-        <v>6556981</v>
+        <v>6556147</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,12 +6287,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,34 +6301,43 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134493920</v>
+        <v>134246129</v>
       </c>
       <c r="B53" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,42 +6345,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325483</v>
+        <v>325208</v>
       </c>
       <c r="R53" t="n">
-        <v>6556127</v>
+        <v>6556981</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6402,12 +6408,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6416,45 +6422,31 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493951</v>
+        <v>134493920</v>
       </c>
       <c r="B54" t="n">
         <v>5181</v>
@@ -6494,10 +6486,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325037</v>
+        <v>325483</v>
       </c>
       <c r="R54" t="n">
-        <v>6557099</v>
+        <v>6556127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6570,16 +6562,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133696603</v>
+        <v>134493951</v>
       </c>
       <c r="B55" t="n">
-        <v>58461</v>
+        <v>5181</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6587,49 +6579,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103018</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325266</v>
+        <v>325037</v>
       </c>
       <c r="R55" t="n">
-        <v>6556841</v>
+        <v>6557099</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6653,12 +6638,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6669,31 +6654,46 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134493919</v>
+        <v>133696603</v>
       </c>
       <c r="B56" t="n">
-        <v>5201</v>
+        <v>58461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,42 +6701,49 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325523</v>
+        <v>325266</v>
       </c>
       <c r="R56" t="n">
-        <v>6556083</v>
+        <v>6556841</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6760,12 +6767,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,43 +6783,28 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493921</v>
+        <v>134493919</v>
       </c>
       <c r="B57" t="n">
         <v>5201</v>
@@ -6852,10 +6844,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325483</v>
+        <v>325523</v>
       </c>
       <c r="R57" t="n">
-        <v>6556127</v>
+        <v>6556083</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6928,13 +6920,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493929</v>
+        <v>134493921</v>
       </c>
       <c r="B58" t="n">
         <v>5201</v>
@@ -6974,10 +6966,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325481</v>
+        <v>325483</v>
       </c>
       <c r="R58" t="n">
-        <v>6556387</v>
+        <v>6556127</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7050,13 +7042,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493932</v>
+        <v>134493929</v>
       </c>
       <c r="B59" t="n">
         <v>5201</v>
@@ -7096,10 +7088,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325436</v>
+        <v>325481</v>
       </c>
       <c r="R59" t="n">
-        <v>6556446</v>
+        <v>6556387</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7172,13 +7164,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493937</v>
+        <v>134493932</v>
       </c>
       <c r="B60" t="n">
         <v>5201</v>
@@ -7218,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325438</v>
+        <v>325436</v>
       </c>
       <c r="R60" t="n">
-        <v>6556553</v>
+        <v>6556446</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7294,16 +7286,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493947</v>
+        <v>134493937</v>
       </c>
       <c r="B61" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7311,21 +7303,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7340,10 +7332,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325197</v>
+        <v>325438</v>
       </c>
       <c r="R61" t="n">
-        <v>6556991</v>
+        <v>6556553</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7389,17 +7381,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7416,16 +7408,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493943</v>
+        <v>134493947</v>
       </c>
       <c r="B62" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,21 +7425,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7462,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325364</v>
+        <v>325197</v>
       </c>
       <c r="R62" t="n">
-        <v>6556631</v>
+        <v>6556991</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7509,6 +7501,21 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7522,6 +7529,113 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493947</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7590,6 +7704,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133659796</v>
+        <v>133696600</v>
       </c>
       <c r="B51" t="n">
-        <v>4776</v>
+        <v>57169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,37 +6119,49 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325488</v>
+        <v>325266</v>
       </c>
       <c r="R51" t="n">
-        <v>6556147</v>
+        <v>6556841</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6173,12 +6185,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6189,38 +6201,28 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134246129</v>
+        <v>133659796</v>
       </c>
       <c r="B52" t="n">
         <v>4776</v>
@@ -6249,25 +6251,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325208</v>
+        <v>325488</v>
       </c>
       <c r="R52" t="n">
-        <v>6556981</v>
+        <v>6556147</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,12 +6287,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6308,34 +6301,43 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134493920</v>
+        <v>134246129</v>
       </c>
       <c r="B53" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,42 +6345,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325483</v>
+        <v>325208</v>
       </c>
       <c r="R53" t="n">
-        <v>6556127</v>
+        <v>6556981</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6402,12 +6408,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6416,45 +6422,31 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493951</v>
+        <v>134493920</v>
       </c>
       <c r="B54" t="n">
         <v>5181</v>
@@ -6494,10 +6486,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325037</v>
+        <v>325483</v>
       </c>
       <c r="R54" t="n">
-        <v>6557099</v>
+        <v>6556127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6570,16 +6562,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133696603</v>
+        <v>134493951</v>
       </c>
       <c r="B55" t="n">
-        <v>58461</v>
+        <v>5181</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6587,49 +6579,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103018</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325266</v>
+        <v>325037</v>
       </c>
       <c r="R55" t="n">
-        <v>6556841</v>
+        <v>6557099</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6653,12 +6638,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6669,31 +6654,46 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134493919</v>
+        <v>133696603</v>
       </c>
       <c r="B56" t="n">
-        <v>5201</v>
+        <v>58461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,42 +6701,49 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325523</v>
+        <v>325266</v>
       </c>
       <c r="R56" t="n">
-        <v>6556083</v>
+        <v>6556841</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6760,12 +6767,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,43 +6783,28 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493921</v>
+        <v>134493919</v>
       </c>
       <c r="B57" t="n">
         <v>5201</v>
@@ -6852,10 +6844,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325483</v>
+        <v>325523</v>
       </c>
       <c r="R57" t="n">
-        <v>6556127</v>
+        <v>6556083</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6928,13 +6920,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493929</v>
+        <v>134493921</v>
       </c>
       <c r="B58" t="n">
         <v>5201</v>
@@ -6974,10 +6966,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325481</v>
+        <v>325483</v>
       </c>
       <c r="R58" t="n">
-        <v>6556387</v>
+        <v>6556127</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7050,13 +7042,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493932</v>
+        <v>134493929</v>
       </c>
       <c r="B59" t="n">
         <v>5201</v>
@@ -7096,10 +7088,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325436</v>
+        <v>325481</v>
       </c>
       <c r="R59" t="n">
-        <v>6556446</v>
+        <v>6556387</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7172,13 +7164,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493937</v>
+        <v>134493932</v>
       </c>
       <c r="B60" t="n">
         <v>5201</v>
@@ -7218,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325438</v>
+        <v>325436</v>
       </c>
       <c r="R60" t="n">
-        <v>6556553</v>
+        <v>6556446</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7294,16 +7286,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493947</v>
+        <v>134493937</v>
       </c>
       <c r="B61" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7311,21 +7303,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7340,10 +7332,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325197</v>
+        <v>325438</v>
       </c>
       <c r="R61" t="n">
-        <v>6556991</v>
+        <v>6556553</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7389,17 +7381,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7416,16 +7408,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493943</v>
+        <v>134493947</v>
       </c>
       <c r="B62" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,21 +7425,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7462,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325364</v>
+        <v>325197</v>
       </c>
       <c r="R62" t="n">
-        <v>6556631</v>
+        <v>6556991</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7509,6 +7501,21 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7522,6 +7529,113 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493947</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7590,6 +7704,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ63"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6108,10 +6108,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133696600</v>
+        <v>133659796</v>
       </c>
       <c r="B51" t="n">
-        <v>57169</v>
+        <v>4776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6119,49 +6119,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325266</v>
+        <v>325488</v>
       </c>
       <c r="R51" t="n">
-        <v>6556841</v>
+        <v>6556147</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6185,12 +6173,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6201,28 +6189,38 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133659796</v>
+        <v>134246129</v>
       </c>
       <c r="B52" t="n">
         <v>4776</v>
@@ -6251,16 +6249,25 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325488</v>
+        <v>325208</v>
       </c>
       <c r="R52" t="n">
-        <v>6556147</v>
+        <v>6556981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6287,12 +6294,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6301,43 +6308,34 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Gran.</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246129</v>
+        <v>134493920</v>
       </c>
       <c r="B53" t="n">
-        <v>4776</v>
+        <v>5181</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6345,46 +6343,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325208</v>
+        <v>325483</v>
       </c>
       <c r="R53" t="n">
-        <v>6556981</v>
+        <v>6556127</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6408,12 +6402,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,31 +6416,45 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493920</v>
+        <v>134493951</v>
       </c>
       <c r="B54" t="n">
         <v>5181</v>
@@ -6486,10 +6494,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325483</v>
+        <v>325037</v>
       </c>
       <c r="R54" t="n">
-        <v>6556127</v>
+        <v>6557099</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6562,16 +6570,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134493951</v>
+        <v>133696603</v>
       </c>
       <c r="B55" t="n">
-        <v>5181</v>
+        <v>58461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6579,42 +6587,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>103018</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325037</v>
+        <v>325266</v>
       </c>
       <c r="R55" t="n">
-        <v>6557099</v>
+        <v>6556841</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6638,12 +6653,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,46 +6669,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133696603</v>
+        <v>134493919</v>
       </c>
       <c r="B56" t="n">
-        <v>58461</v>
+        <v>5201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,49 +6701,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103018</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325266</v>
+        <v>325523</v>
       </c>
       <c r="R56" t="n">
-        <v>6556841</v>
+        <v>6556083</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,12 +6760,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6783,28 +6776,43 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493919</v>
+        <v>134493921</v>
       </c>
       <c r="B57" t="n">
         <v>5201</v>
@@ -6844,10 +6852,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325523</v>
+        <v>325483</v>
       </c>
       <c r="R57" t="n">
-        <v>6556083</v>
+        <v>6556127</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6920,13 +6928,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493921</v>
+        <v>134493929</v>
       </c>
       <c r="B58" t="n">
         <v>5201</v>
@@ -6966,10 +6974,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>325483</v>
+        <v>325481</v>
       </c>
       <c r="R58" t="n">
-        <v>6556127</v>
+        <v>6556387</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7042,13 +7050,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493929</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493929</v>
+        <v>134493932</v>
       </c>
       <c r="B59" t="n">
         <v>5201</v>
@@ -7088,10 +7096,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325481</v>
+        <v>325436</v>
       </c>
       <c r="R59" t="n">
-        <v>6556387</v>
+        <v>6556446</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7164,13 +7172,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493932</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493932</v>
+        <v>134493937</v>
       </c>
       <c r="B60" t="n">
         <v>5201</v>
@@ -7210,10 +7218,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325436</v>
+        <v>325438</v>
       </c>
       <c r="R60" t="n">
-        <v>6556446</v>
+        <v>6556553</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7286,16 +7294,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/134493937</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493937</v>
+        <v>134493947</v>
       </c>
       <c r="B61" t="n">
-        <v>5201</v>
+        <v>8460</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7303,21 +7311,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7332,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325438</v>
+        <v>325197</v>
       </c>
       <c r="R61" t="n">
-        <v>6556553</v>
+        <v>6556991</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7381,17 +7389,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7408,16 +7416,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493947</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493947</v>
+        <v>134493943</v>
       </c>
       <c r="B62" t="n">
-        <v>8460</v>
+        <v>8449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,21 +7433,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7454,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325197</v>
+        <v>325364</v>
       </c>
       <c r="R62" t="n">
-        <v>6556991</v>
+        <v>6556631</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7501,21 +7509,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7529,113 +7522,6 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>134493943</v>
-      </c>
-      <c r="B63" t="n">
-        <v>8449</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Mellanfjällen, Dls</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>325364</v>
-      </c>
-      <c r="R63" t="n">
-        <v>6556631</v>
-      </c>
-      <c r="S63" t="n">
-        <v>5</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7704,7 +7590,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22139-2026 artfynd.xlsx
+++ b/artfynd/A 22139-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ63"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3334,10 +3334,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134287964</v>
+        <v>136582848</v>
       </c>
       <c r="B26" t="n">
-        <v>92013</v>
+        <v>91111</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325404</v>
+        <v>325181</v>
       </c>
       <c r="R26" t="n">
-        <v>6556569</v>
+        <v>6556932</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3406,12 +3406,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Låga med markkontakt, på undersidan # Pinus sylvestris</t>
+          <t>Låga med markkontakt, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3458,51 +3458,58 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134287964</t>
+          <t>https://artportalen.se/Sighting/136582848</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133657368</v>
+        <v>134287964</v>
       </c>
       <c r="B27" t="n">
-        <v>96783</v>
+        <v>92013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mardyveln, i brant V om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325446</v>
+        <v>325404</v>
       </c>
       <c r="R27" t="n">
-        <v>6556299</v>
+        <v>6556569</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,17 +3536,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Många riktigt stora tuvor mellan branten och tjärnet.</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3548,66 +3550,85 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt, på undersidan # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657368</t>
+          <t>https://artportalen.se/Sighting/134287964</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134246151</v>
+        <v>136583910</v>
       </c>
       <c r="B28" t="n">
-        <v>97810</v>
+        <v>92155</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2569</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3615,10 +3636,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>325171</v>
+        <v>325416</v>
       </c>
       <c r="R28" t="n">
-        <v>6556959</v>
+        <v>6556561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3645,12 +3666,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,30 +3684,50 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Låga, undersidan # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246151</t>
+          <t>https://artportalen.se/Sighting/136583910</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133657369</v>
+        <v>133657368</v>
       </c>
       <c r="B29" t="n">
-        <v>97471</v>
+        <v>96783</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,21 +3735,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3718,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>325441</v>
+        <v>325446</v>
       </c>
       <c r="R29" t="n">
-        <v>6556279</v>
+        <v>6556299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3756,6 +3797,11 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Många riktigt stora tuvor mellan branten och tjärnet.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3768,11 +3814,6 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3789,16 +3830,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657369</t>
+          <t>https://artportalen.se/Sighting/133657368</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134493923</v>
+        <v>134246151</v>
       </c>
       <c r="B30" t="n">
-        <v>97471</v>
+        <v>97810</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,37 +3847,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>325481</v>
+        <v>325171</v>
       </c>
       <c r="R30" t="n">
-        <v>6556144</v>
+        <v>6556959</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3860,12 +3905,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,30 +3919,31 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493923</t>
+          <t>https://artportalen.se/Sighting/134246151</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134493927</v>
+        <v>133657369</v>
       </c>
       <c r="B31" t="n">
         <v>97471</v>
@@ -3928,17 +3974,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, i brant V om, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>325443</v>
+        <v>325441</v>
       </c>
       <c r="R31" t="n">
-        <v>6556199</v>
+        <v>6556279</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3962,12 +4008,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3979,45 +4025,40 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493927</t>
+          <t>https://artportalen.se/Sighting/133657369</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133657362</v>
+        <v>134493923</v>
       </c>
       <c r="B32" t="n">
-        <v>97873</v>
+        <v>97471</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,37 +4066,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2609</v>
+        <v>2590</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325499</v>
+        <v>325481</v>
       </c>
       <c r="R32" t="n">
-        <v>6556462</v>
+        <v>6556144</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4079,12 +4120,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,36 +4136,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Bergbrant i barrskog.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657362</t>
+          <t>https://artportalen.se/Sighting/134493923</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133657365</v>
+        <v>134493927</v>
       </c>
       <c r="B33" t="n">
-        <v>96512</v>
+        <v>97471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4132,37 +4168,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2667</v>
+        <v>2590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>325499</v>
+        <v>325443</v>
       </c>
       <c r="R33" t="n">
-        <v>6556462</v>
+        <v>6556199</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4186,12 +4222,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4203,73 +4239,80 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Bergbrant i barrskog.</t>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657365</t>
+          <t>https://artportalen.se/Sighting/134493927</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133657355</v>
+        <v>133657362</v>
       </c>
       <c r="B34" t="n">
-        <v>93271</v>
+        <v>97873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>2609</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
+          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>325121</v>
+        <v>325499</v>
       </c>
       <c r="R34" t="n">
-        <v>6556881</v>
+        <v>6556462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4310,13 +4353,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Bergbrant i barrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4327,60 +4369,57 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657355</t>
+          <t>https://artportalen.se/Sighting/133657362</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134245975</v>
+        <v>133657365</v>
       </c>
       <c r="B35" t="n">
-        <v>93271</v>
+        <v>96512</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>2667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, bergbrant ca 100 m norr om, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>325056</v>
+        <v>325499</v>
       </c>
       <c r="R35" t="n">
-        <v>6557097</v>
+        <v>6556462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4407,17 +4446,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4426,31 +4460,35 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Bergbrant i barrskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134245975</t>
+          <t>https://artportalen.se/Sighting/133657365</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134493938</v>
+        <v>133657355</v>
       </c>
       <c r="B36" t="n">
         <v>93271</v>
@@ -4479,19 +4517,22 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>325374</v>
+        <v>325121</v>
       </c>
       <c r="R36" t="n">
-        <v>6556523</v>
+        <v>6556881</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4515,12 +4556,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4529,30 +4570,36 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493938</t>
+          <t>https://artportalen.se/Sighting/133657355</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134493945</v>
+        <v>134245975</v>
       </c>
       <c r="B37" t="n">
         <v>93271</v>
@@ -4581,19 +4628,22 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>325222</v>
+        <v>325056</v>
       </c>
       <c r="R37" t="n">
-        <v>6556974</v>
+        <v>6557097</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4617,12 +4667,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4631,30 +4686,31 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493945</t>
+          <t>https://artportalen.se/Sighting/134245975</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134493946</v>
+        <v>134493938</v>
       </c>
       <c r="B38" t="n">
         <v>93271</v>
@@ -4689,10 +4745,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>325214</v>
+        <v>325374</v>
       </c>
       <c r="R38" t="n">
-        <v>6556988</v>
+        <v>6556523</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4750,13 +4806,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493946</t>
+          <t>https://artportalen.se/Sighting/134493938</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134493948</v>
+        <v>134493945</v>
       </c>
       <c r="B39" t="n">
         <v>93271</v>
@@ -4791,10 +4847,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>325140</v>
+        <v>325222</v>
       </c>
       <c r="R39" t="n">
-        <v>6557024</v>
+        <v>6556974</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4852,13 +4908,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493948</t>
+          <t>https://artportalen.se/Sighting/134493945</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134493950</v>
+        <v>134493946</v>
       </c>
       <c r="B40" t="n">
         <v>93271</v>
@@ -4893,10 +4949,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>325105</v>
+        <v>325214</v>
       </c>
       <c r="R40" t="n">
-        <v>6557056</v>
+        <v>6556988</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4954,16 +5010,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493950</t>
+          <t>https://artportalen.se/Sighting/134493946</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134493939</v>
+        <v>134493948</v>
       </c>
       <c r="B41" t="n">
-        <v>91995</v>
+        <v>93271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4971,21 +5027,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4995,10 +5051,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>325361</v>
+        <v>325140</v>
       </c>
       <c r="R41" t="n">
-        <v>6556573</v>
+        <v>6557024</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5042,21 +5098,6 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
@@ -5071,38 +5112,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493939</t>
+          <t>https://artportalen.se/Sighting/134493948</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134493930</v>
+        <v>134493950</v>
       </c>
       <c r="B42" t="n">
-        <v>91937</v>
+        <v>93271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5112,10 +5153,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>325481</v>
+        <v>325105</v>
       </c>
       <c r="R42" t="n">
-        <v>6556387</v>
+        <v>6557056</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5159,21 +5200,6 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
@@ -5188,16 +5214,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493930</t>
+          <t>https://artportalen.se/Sighting/134493950</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134245897</v>
+        <v>134493939</v>
       </c>
       <c r="B43" t="n">
-        <v>75468</v>
+        <v>91995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5205,37 +5231,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ravin nordväst, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>325008</v>
+        <v>325361</v>
       </c>
       <c r="R43" t="n">
-        <v>6557270</v>
+        <v>6556573</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5262,12 +5285,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5276,75 +5299,86 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134245897</t>
+          <t>https://artportalen.se/Sighting/134493939</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134246089</v>
+        <v>134493930</v>
       </c>
       <c r="B44" t="n">
-        <v>79992</v>
+        <v>91937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>325136</v>
+        <v>325481</v>
       </c>
       <c r="R44" t="n">
-        <v>6557020</v>
+        <v>6556387</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5368,12 +5402,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5382,62 +5416,80 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246089</t>
+          <t>https://artportalen.se/Sighting/134493930</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134288659</v>
+        <v>136582995</v>
       </c>
       <c r="B45" t="n">
-        <v>79992</v>
+        <v>92780</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5448,10 +5500,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>325338</v>
+        <v>325183</v>
       </c>
       <c r="R45" t="n">
-        <v>6556520</v>
+        <v>6556846</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,12 +5530,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5501,21 +5553,6 @@
           <t>Barrblandskog</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -5530,16 +5567,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134288659</t>
+          <t>https://artportalen.se/Sighting/136582995</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134493940</v>
+        <v>134245897</v>
       </c>
       <c r="B46" t="n">
-        <v>79992</v>
+        <v>75468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5547,34 +5584,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ravin nordväst, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>325365</v>
+        <v>325008</v>
       </c>
       <c r="R46" t="n">
-        <v>6556582</v>
+        <v>6557270</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5601,12 +5641,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5615,45 +5655,31 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493940</t>
+          <t>https://artportalen.se/Sighting/134245897</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134493949</v>
+        <v>134246089</v>
       </c>
       <c r="B47" t="n">
         <v>79992</v>
@@ -5682,19 +5708,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>325128</v>
+        <v>325136</v>
       </c>
       <c r="R47" t="n">
-        <v>6557028</v>
+        <v>6557020</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5718,12 +5747,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5732,83 +5761,76 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493949</t>
+          <t>https://artportalen.se/Sighting/134246089</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133657356</v>
+        <v>134288659</v>
       </c>
       <c r="B48" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>325284</v>
+        <v>325338</v>
       </c>
       <c r="R48" t="n">
-        <v>6556743</v>
+        <v>6556520</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5835,17 +5857,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5854,76 +5871,92 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Tallskog.</t>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657356</t>
+          <t>https://artportalen.se/Sighting/134288659</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133657357</v>
+        <v>134493940</v>
       </c>
       <c r="B49" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>325321</v>
+        <v>325365</v>
       </c>
       <c r="R49" t="n">
-        <v>6556585</v>
+        <v>6556582</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5947,17 +5980,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i stående dött träd.</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,85 +5997,83 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Tallskog.</t>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657357</t>
+          <t>https://artportalen.se/Sighting/134493940</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134246027</v>
+        <v>134493949</v>
       </c>
       <c r="B50" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>325114</v>
+        <v>325128</v>
       </c>
       <c r="R50" t="n">
-        <v>6557125</v>
+        <v>6557028</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6071,12 +6097,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6087,67 +6113,77 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246027</t>
+          <t>https://artportalen.se/Sighting/134493949</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133696600</v>
+        <v>136583741</v>
       </c>
       <c r="B51" t="n">
-        <v>57169</v>
+        <v>80093</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6155,13 +6191,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>325266</v>
+        <v>325124</v>
       </c>
       <c r="R51" t="n">
-        <v>6556841</v>
+        <v>6557001</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6185,12 +6221,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6199,33 +6235,54 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696600</t>
+          <t>https://artportalen.se/Sighting/136583741</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133659796</v>
+        <v>133657356</v>
       </c>
       <c r="B52" t="n">
-        <v>4776</v>
+        <v>57972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6233,34 +6290,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mardyveln, ca 20 m SSV om, Dls</t>
+          <t>Mellanfjällen, ca 450 m NNV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>325488</v>
+        <v>325284</v>
       </c>
       <c r="R52" t="n">
-        <v>6556147</v>
+        <v>6556743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6295,6 +6352,11 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6306,12 +6368,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Gran.</t>
+          <t>Tallskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6322,22 +6379,22 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133659796</t>
+          <t>https://artportalen.se/Sighting/133657356</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134246129</v>
+        <v>133657357</v>
       </c>
       <c r="B53" t="n">
-        <v>4776</v>
+        <v>57972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6345,43 +6402,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mellanfjällen, ca 300 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>325208</v>
+        <v>325321</v>
       </c>
       <c r="R53" t="n">
-        <v>6556981</v>
+        <v>6556585</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6408,12 +6456,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i stående dött träd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6422,34 +6475,38 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246129</t>
+          <t>https://artportalen.se/Sighting/133657357</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134493920</v>
+        <v>134246027</v>
       </c>
       <c r="B54" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6457,42 +6514,49 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>325483</v>
+        <v>325114</v>
       </c>
       <c r="R54" t="n">
-        <v>6556127</v>
+        <v>6557125</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6516,12 +6580,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6532,46 +6596,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493920</t>
+          <t>https://artportalen.se/Sighting/134246027</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134493951</v>
+        <v>133696600</v>
       </c>
       <c r="B55" t="n">
-        <v>5181</v>
+        <v>57169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6579,42 +6628,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>325037</v>
+        <v>325266</v>
       </c>
       <c r="R55" t="n">
-        <v>6557099</v>
+        <v>6556841</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6638,12 +6694,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6654,46 +6710,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/133696600</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133696603</v>
+        <v>133659796</v>
       </c>
       <c r="B56" t="n">
-        <v>58461</v>
+        <v>4776</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6701,49 +6742,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103018</v>
+        <v>100299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Mardyveln, ca 20 m SSV om, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>325266</v>
+        <v>325488</v>
       </c>
       <c r="R56" t="n">
-        <v>6556841</v>
+        <v>6556147</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6767,12 +6796,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6783,31 +6812,41 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Gran.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696603</t>
+          <t>https://artportalen.se/Sighting/133659796</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134493919</v>
+        <v>134246129</v>
       </c>
       <c r="B57" t="n">
-        <v>5201</v>
+        <v>4776</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6815,42 +6854,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>325523</v>
+        <v>325208</v>
       </c>
       <c r="R57" t="n">
-        <v>6556083</v>
+        <v>6556981</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6874,12 +6917,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6888,48 +6931,34 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493919</t>
+          <t>https://artportalen.se/Sighting/134246129</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134493921</v>
+        <v>134493920</v>
       </c>
       <c r="B58" t="n">
-        <v>5201</v>
+        <v>5181</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,21 +6966,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7042,16 +7071,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493921</t>
+          <t>https://artportalen.se/Sighting/134493920</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134493929</v>
+        <v>134493951</v>
       </c>
       <c r="B59" t="n">
-        <v>5201</v>
+        <v>5181</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7059,21 +7088,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7088,10 +7117,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>325481</v>
+        <v>325037</v>
       </c>
       <c r="R59" t="n">
-        <v>6556387</v>
+        <v>6557099</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7164,16 +7193,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493929</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134493932</v>
+        <v>133696603</v>
       </c>
       <c r="B60" t="n">
-        <v>5201</v>
+        <v>58461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7181,42 +7210,49 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>103018</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>325436</v>
+        <v>325266</v>
       </c>
       <c r="R60" t="n">
-        <v>6556446</v>
+        <v>6556841</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7240,12 +7276,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7256,43 +7292,28 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493932</t>
+          <t>https://artportalen.se/Sighting/133696603</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134493937</v>
+        <v>134493919</v>
       </c>
       <c r="B61" t="n">
         <v>5201</v>
@@ -7332,10 +7353,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>325438</v>
+        <v>325523</v>
       </c>
       <c r="R61" t="n">
-        <v>6556553</v>
+        <v>6556083</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7408,16 +7429,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493937</t>
+          <t>https://artportalen.se/Sighting/134493919</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134493947</v>
+        <v>134493921</v>
       </c>
       <c r="B62" t="n">
-        <v>8460</v>
+        <v>5201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,21 +7446,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7454,10 +7475,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>325197</v>
+        <v>325483</v>
       </c>
       <c r="R62" t="n">
-        <v>6556991</v>
+        <v>6556127</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7503,17 +7524,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7530,16 +7551,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493947</t>
+          <t>https://artportalen.se/Sighting/134493921</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134493943</v>
+        <v>134493929</v>
       </c>
       <c r="B63" t="n">
-        <v>8449</v>
+        <v>5201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7547,21 +7568,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7576,10 +7597,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>325364</v>
+        <v>325481</v>
       </c>
       <c r="R63" t="n">
-        <v>6556631</v>
+        <v>6556387</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7623,6 +7644,21 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
@@ -7636,6 +7672,479 @@
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493929</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134493932</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>325436</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6556446</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493932</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134493937</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>325438</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6556553</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493937</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134493947</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>325197</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6556991</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493947</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134493943</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>325364</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6556631</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134493943</t>
         </is>
@@ -7705,6 +8214,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
